--- a/stories/arbres/ATOM-EMO.LEX.010-07.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.010-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Honoré est au jardin avec maman. L'arrosoir est lourd. Honoré le porte jusqu'au bac. C'est un effort. Il pose l'arrosoir. Il sent sa poitrine chaude. Il dit : je suis fier. Fier de mon effort. Maman sourit. Maman dit : tu as fait un effort. Honoré répète : fier. Plus tard, il aligne les pots. Encore un effort. Il dit encore : je suis fier de mon effort. Maman l'écoute. Être fier, ce n'est pas rabaisser l'autre. C'est content d'un effort.</t>
+          <t>Honoré est au jardin avec maman. L'arrosoir est lourd. Honoré le porte jusqu'au bac. C'est un effort. Il pose l'arrosoir. Il sent sa poitrine chaude. Je suis fier. Fier de mon effort. Maman sourit. Tu as fait un effort. Honoré répète : fier. Plus tard, il aligne les pots. Encore un effort. Il dit encore : je suis fier de mon effort. Maman l'écoute. Être fier, ce n'est pas rabaisser l'autre. C'est content d'un effort.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Honoré est au jardin avec maman. L'arrosoir est lourd. Honoré le porte jusqu'au bac. C'est un effort. Il pose l'arrosoir. Il sent sa poitrine chaude.
+narrateur|Je suis fier. Fier de mon effort. Maman sourit.
+maman|Tu as fait un effort.
+narrateur|Honoré répète : fier. Plus tard, il aligne les pots. Encore un effort. Il dit encore : je suis fier de mon effort. Maman l'écoute. Être fier, ce n'est pas rabaisser l'autre. C'est content d'un effort.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1489,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Honoré porte l'arrosoir. Que dit-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1662,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Honoré a nommé : fier. Il a fait un effort. Maman a écouté.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1829,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Honoré prend la main de maman. Ils rentrent.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1996,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2036,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.010-07.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.010-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,7 @@
 narrateur|Honoré répète : fier. Plus tard, il aligne les pots. Encore un effort. Il dit encore : je suis fier de mon effort. Maman l'écoute. Être fier, ce n'est pas rabaisser l'autre. C'est content d'un effort.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1496,6 +1502,7 @@
           <t>narrateur|Honoré porte l'arrosoir. Que dit-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1667,6 +1674,7 @@
           <t>narrateur|Honoré a nommé : fier. Il a fait un effort. Maman a écouté.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1842,7 @@
           <t>narrateur|Honoré prend la main de maman. Ils rentrent.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2019,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2053,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2244,6 +2268,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.010-07.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.010-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Honoré est fier de son effort</t>
+          <t>L'arrosoir de Mila</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mila porte l'arrosoir lourd jusqu'au bac. Elle est fière de son effort. Elle aligne les pots. Encore fière.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Honoré est au jardin avec maman. L'arrosoir est lourd. Honoré le porte jusqu'au bac. C'est un effort. Il pose l'arrosoir. Il sent sa poitrine chaude. Je suis fier. Fier de mon effort. Maman sourit. Tu as fait un effort. Honoré répète : fier. Plus tard, il aligne les pots. Encore un effort. Il dit encore : je suis fier de mon effort. Maman l'écoute. Être fier, ce n'est pas rabaisser l'autre. C'est content d'un effort.</t>
+          <t>Un escargot avance sur une feuille. Sa trace brille, toute fine. Les tomates sentent le soleil. Une abeille passe, tout près, puis plus. La terre du bac est sombre, un peu sèche. L'arrosoir vert attend près du mur. Mila, tu as vu l'escargot ? Oui, maman. Il va tout lentement. Comme nous, avec l'arrosoir. Pas trop vite. En ce moment, Mila prend l'arrosoir. Il est lourd. L'eau bouge dedans. Il est lourd, maman. Tu le portes jusqu'au bac. Tout doux. Mila porte l'arrosoir. Ses bras travaillent. Ses pieds vont lentement. Elle pose l'arrosoir près du bac. Il est arrivé. Jusqu'au bac. Tu as fait un effort. Mila sent sa poitrine chaude. Elle se tient droite, près des tomates. Je suis fière. Fière de mon effort. Tu as fait un effort. Bravo, Mila. C'est du bon travail. Fière. Être fière, ce n'est pas rabaisser l'autre. C'est content d'un effort. Content d'un effort. Oui. Tu verses un peu d'eau, maintenant ? Un peu. Pour les tomates. L'eau fait un cercle sombre. La terre boit, tout doucement. Plus tard, on aligne les pots ? Oui. Les petits pots, en rang. Mila aligne les pots, un par un. Le terre cuite est chaude sous les doigts. Je suis fière de mon effort. Encore. L'arrosoir, puis les pots. Je t'écoute. Tu as nommé : fière. Pas rabaisser l'autre. Mon effort. Oui. Bravo. Du bon travail. L'escargot est encore sur la feuille ? Oui. Il avance encore. Nous aussi. Tout doux. Les tomates ont de l'eau, maintenant ? Oui. La terre est sombre. Ton effort a porté jusqu'au bac. L'arrosoir vert reste près du bac. Les pots sont en rang, tout droits. Une abeille passe encore, loin. La trace de l'escargot brille encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,13 +1324,64 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Honoré est au jardin avec maman. L'arrosoir est lourd. Honoré le porte jusqu'au bac. C'est un effort. Il pose l'arrosoir. Il sent sa poitrine chaude.
-narrateur|Je suis fier. Fier de mon effort. Maman sourit.
+          <t>narrateur|Un escargot avance sur une feuille.
+narrateur|Sa trace brille, toute fine.
+narrateur|Les tomates sentent le soleil.
+narrateur|Une abeille passe, tout près, puis plus.
+narrateur|La terre du bac est sombre, un peu sèche.
+narrateur|L'arrosoir vert attend près du mur.
+maman|Mila, tu as vu l'escargot ?
+enfant-f|Oui, maman. Il va tout lentement.
+maman|Comme nous, avec l'arrosoir. Pas trop vite.
+narrateur|En ce moment, Mila prend l'arrosoir.
+narrateur|Il est lourd. L'eau bouge dedans.
+enfant-f|Il est lourd, maman.
+maman|Tu le portes jusqu'au bac. Tout doux.
+narrateur|Mila porte l'arrosoir.
+narrateur|Ses bras travaillent. Ses pieds vont lentement.
+narrateur|Elle pose l'arrosoir près du bac.
+enfant-f|Il est arrivé. Jusqu'au bac.
 maman|Tu as fait un effort.
-narrateur|Honoré répète : fier. Plus tard, il aligne les pots. Encore un effort. Il dit encore : je suis fier de mon effort. Maman l'écoute. Être fier, ce n'est pas rabaisser l'autre. C'est content d'un effort.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+narrateur|Mila sent sa poitrine chaude.
+narrateur|Elle se tient droite, près des tomates.
+enfant-f|Je suis fière.
+enfant-f|Fière de mon effort.
+maman|Tu as fait un effort. Bravo, Mila.
+maman|C'est du bon travail.
+enfant-f|Fière.
+maman|Être fière, ce n'est pas rabaisser l'autre.
+maman|C'est content d'un effort.
+enfant-f|Content d'un effort. Oui.
+maman|Tu verses un peu d'eau, maintenant ?
+enfant-f|Un peu. Pour les tomates.
+narrateur|L'eau fait un cercle sombre.
+narrateur|La terre boit, tout doucement.
+maman|Plus tard, on aligne les pots ?
+enfant-f|Oui. Les petits pots, en rang.
+narrateur|Mila aligne les pots, un par un.
+narrateur|Le terre cuite est chaude sous les doigts.
+enfant-f|Je suis fière de mon effort.
+maman|Encore. L'arrosoir, puis les pots.
+maman|Je t'écoute. Tu as nommé : fière.
+enfant-f|Pas rabaisser l'autre. Mon effort.
+maman|Oui. Bravo. Du bon travail.
+maman|L'escargot est encore sur la feuille ?
+enfant-f|Oui. Il avance encore.
+maman|Nous aussi. Tout doux.
+maman|Les tomates ont de l'eau, maintenant ?
+enfant-f|Oui. La terre est sombre.
+maman|Ton effort a porté jusqu'au bac.
+narrateur|L'arrosoir vert reste près du bac.
+narrateur|Les pots sont en rang, tout droits.
+narrateur|Une abeille passe encore, loin.
+narrateur|La trace de l'escargot brille encore.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>jardin,arrosoir,abeille</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1343,7 +1406,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Honoré porte l'arrosoir. Que dit-il ?</t>
+          <t>Mila porte l'arrosoir. Que dit-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1499,7 +1562,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Honoré porte l'arrosoir. Que dit-il ?</t>
+          <t>narrateur|Mila porte l'arrosoir.
+narrateur|Que dit-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1527,7 +1591,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Honoré a nommé : fier. Il a fait un effort. Maman a écouté.</t>
+          <t>Mila a nommé : fière. Elle a fait un effort. Maman a écouté. Je suis fière de mon effort. Oui. Tu as porté l'arrosoir. Bravo. C'est du bon travail. Puis les pots. Encore un effort. Être fière, c'est content d'un effort. Tu veux encore dire le mot ? Fière. Les pots restent en rang. La terre du bac est sombre, maintenant.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1671,10 +1735,25 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Honoré a nommé : fier. Il a fait un effort. Maman a écouté.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Mila a nommé : fière.
+narrateur|Elle a fait un effort.
+narrateur|Maman a écouté.
+enfant-f|Je suis fière de mon effort.
+maman|Oui. Tu as porté l'arrosoir.
+maman|Bravo. C'est du bon travail.
+enfant-f|Puis les pots. Encore un effort.
+maman|Être fière, c'est content d'un effort.
+maman|Tu veux encore dire le mot ?
+enfant-f|Fière.
+narrateur|Les pots restent en rang.
+narrateur|La terre du bac est sombre, maintenant.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>jardin,pots</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1699,7 +1778,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Honoré prend la main de maman. Ils rentrent.</t>
+          <t>Mila prend la main de maman. On rentre ? L'arrosoir reste ici. Oui. Il est moins lourd, vide. Tu as porté. Tu as aligné. Je suis encore fière. Bravo, Mila. Ils rentrent. L'escargot est encore sur sa feuille. Les tomates sentent toujours le soleil.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1839,10 +1918,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Honoré prend la main de maman. Ils rentrent.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Mila prend la main de maman.
+maman|On rentre ? L'arrosoir reste ici.
+enfant-f|Oui. Il est moins lourd, vide.
+maman|Tu as porté. Tu as aligné.
+enfant-f|Je suis encore fière.
+maman|Bravo, Mila.
+narrateur|Ils rentrent.
+narrateur|L'escargot est encore sur sa feuille.
+narrateur|Les tomates sentent toujours le soleil.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>jardin</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1867,7 +1958,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'étais fière de mon effort. L'arrosoir, puis les pots. Bravo. L'arrosoir vert reste près du bac. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2007,7 +2098,10 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'étais fière de mon effort.
+maman|L'arrosoir, puis les pots. Bravo.
+narrateur|L'arrosoir vert reste près du bac.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2029,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2067,6 +2161,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.010-07.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.010-07.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un escargot avance sur une feuille. Sa trace brille, toute fine. Les tomates sentent le soleil. Une abeille passe, tout près, puis plus. La terre du bac est sombre, un peu sèche. L'arrosoir vert attend près du mur. Mila, tu as vu l'escargot ? Oui, maman. Il va tout lentement. Comme nous, avec l'arrosoir. Pas trop vite. En ce moment, Mila prend l'arrosoir. Il est lourd. L'eau bouge dedans. Il est lourd, maman. Tu le portes jusqu'au bac. Tout doux. Mila porte l'arrosoir. Ses bras travaillent. Ses pieds vont lentement. Elle pose l'arrosoir près du bac. Il est arrivé. Jusqu'au bac. Tu as fait un effort. Mila sent sa poitrine chaude. Elle se tient droite, près des tomates. Je suis fière. Fière de mon effort. Tu as fait un effort. Bravo, Mila. C'est du bon travail. Fière. Être fière, ce n'est pas rabaisser l'autre. C'est content d'un effort. Content d'un effort. Oui. Tu verses un peu d'eau, maintenant ? Un peu. Pour les tomates. L'eau fait un cercle sombre. La terre boit, tout doucement. Plus tard, on aligne les pots ? Oui. Les petits pots, en rang. Mila aligne les pots, un par un. Le terre cuite est chaude sous les doigts. Je suis fière de mon effort. Encore. L'arrosoir, puis les pots. Je t'écoute. Tu as nommé : fière. Pas rabaisser l'autre. Mon effort. Oui. Bravo. Du bon travail. L'escargot est encore sur la feuille ? Oui. Il avance encore. Nous aussi. Tout doux. Les tomates ont de l'eau, maintenant ? Oui. La terre est sombre. Ton effort a porté jusqu'au bac. L'arrosoir vert reste près du bac. Les pots sont en rang, tout droits. Une abeille passe encore, loin. La trace de l'escargot brille encore.</t>
+          <t>Un escargot avance sur une feuille. Sa trace brille, toute fine. Les tomates sentent le soleil. Une abeille passe, tout près, puis plus. La terre du bac est sombre, un peu sèche. L'arrosoir vert attend près du mur. Mila, tu as vu l'escargot ? Oui, maman. Il va tout lentement. Comme nous, avec l'arrosoir. Pas trop vite. En ce moment, Mila prend l'arrosoir. Il est lourd. L'eau bouge dedans. Il est lourd, maman. Tu le portes jusqu'au bac. Tout doux. Mila porte l'arrosoir. Ses bras travaillent. Ses pieds vont lentement. Elle pose l'arrosoir près du bac. Il est arrivé. Jusqu'au bac. Tu as fait un effort. Mila sent sa poitrine chaude. Elle se tient droite, près des tomates. Je suis fière. Fière de mon effort. Tu as fait un effort. Bravo, Mila. Fière. Être fière, ce n'est pas rabaisser l'autre. C'est content d'un effort. Content d'un effort. Oui. Tu verses un peu d'eau, maintenant ? Un peu. Pour les tomates. L'eau fait un cercle sombre. La terre boit, tout doucement. Plus tard, on aligne les pots ? Oui. Les petits pots, en rang. Mila aligne les pots, un par un. Le terre cuite est chaude sous les doigts. Je suis fière de mon effort. Encore. L'arrosoir, puis les pots. Je t'écoute. Tu as nommé : fière. Pas rabaisser l'autre. Mon effort. Oui. Bravo. Du bon travail. L'escargot est encore sur la feuille ? Oui. Il avance encore. Nous aussi. Tout doux. Les tomates ont de l'eau, maintenant ? Oui. La terre est sombre. Ton effort a porté jusqu'au bac. L'arrosoir vert reste près du bac. Les pots sont en rang, tout droits. Une abeille passe encore, loin. La trace de l'escargot brille encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Honoré est au jardin avec maman. L'arrosoir est lourd. Honoré le porte jusqu'au bac. C'est un effort. Il pose l'arrosoir. Il sent sa poitrine chaude. Il dit : je suis &lt;emphasis level="moderate"&gt;fier&lt;/emphasis&gt;. Fier de mon effort. Maman sourit. Maman dit : tu as fait un effort. Honoré répète : fier. Plus tard, il aligne les pots. Encore un effort. Il dit encore : je suis fier de mon effort. Maman l'écoute. Être fier, ce n'est pas rabaisser l'autre. C'est content d'un effort.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un escargot avance sur une feuille. Sa trace brille, toute fine. Les tomates sentent le soleil. Une abeille passe, tout près, puis plus. La terre du bac est sombre, un peu sèche. L'arrosoir vert attend près du mur. Mila, tu as vu l'escargot ? Oui, maman. Il va tout lentement. Comme nous, avec l'arrosoir. Pas trop vite. En ce moment, Mila prend l'arrosoir. Il est lourd. L'eau bouge dedans. Il est lourd, maman. Tu le portes jusqu'au bac. Tout doux. Mila porte l'arrosoir. Ses bras travaillent. Ses pieds vont lentement. Elle pose l'arrosoir près du bac. Il est arrivé. Jusqu'au bac. Tu as fait un effort. Mila sent sa poitrine chaude. Elle se tient droite, près des tomates. Je suis fière. Fière de mon effort. Tu as fait un effort. Bravo, Mila. Fière. Être fière, ce n'est pas rabaisser l'autre. C'est content d'un effort. Content d'un effort. Oui. Tu verses un peu d'eau, maintenant ? Un peu. Pour les tomates. L'eau fait un cercle sombre. La terre boit, tout doucement. Plus tard, on aligne les pots ? Oui. Les petits pots, en rang. Mila aligne les pots, un par un. Le terre cuite est chaude sous les doigts. Je suis fière de mon effort. Encore. L'arrosoir, puis les pots. Je t'écoute. Tu as nommé : fière. Pas rabaisser l'autre. Mon effort. Oui. Bravo. Du bon travail. L'escargot est encore sur la feuille ? Oui. Il avance encore. Nous aussi. Tout doux. Les tomates ont de l'eau, maintenant ? Oui. La terre est sombre. Ton effort a porté jusqu'au bac. L'arrosoir vert reste près du bac. Les pots sont en rang, tout droits. Une abeille passe encore, loin. La trace de l'escargot brille encore.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1347,7 +1347,6 @@
 enfant-f|Je suis fière.
 enfant-f|Fière de mon effort.
 maman|Tu as fait un effort. Bravo, Mila.
-maman|C'est du bon travail.
 enfant-f|Fière.
 maman|Être fière, ce n'est pas rabaisser l'autre.
 maman|C'est content d'un effort.
@@ -1411,7 +1410,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Honoré porte l'arrosoir. Que dit-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila porte l'arrosoir. Que dit-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1566,7 +1565,6 @@
 narrateur|Que dit-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1591,12 +1589,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila a nommé : fière. Elle a fait un effort. Maman a écouté. Je suis fière de mon effort. Oui. Tu as porté l'arrosoir. Bravo. C'est du bon travail. Puis les pots. Encore un effort. Être fière, c'est content d'un effort. Tu veux encore dire le mot ? Fière. Les pots restent en rang. La terre du bac est sombre, maintenant.</t>
+          <t>Mila a nommé : fière. Elle a fait un effort. Maman a écouté. Je suis fière de mon effort. Oui. Tu as porté l'arrosoir. Puis les pots. Encore un effort. Être fière, c'est content d'un effort. Tu veux encore dire le mot ? Fière. Les pots restent en rang. La terre du bac est sombre, maintenant.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Honoré a nommé : &lt;emphasis level="moderate"&gt;fier&lt;/emphasis&gt;. Il a fait un effort. Maman a écouté.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a nommé : fière. Elle a fait un effort. Maman a écouté. Je suis fière de mon effort. Oui. Tu as porté l'arrosoir. Puis les pots. Encore un effort. Être fière, c'est content d'un effort. Tu veux encore dire le mot ? Fière. Les pots restent en rang. La terre du bac est sombre, maintenant.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1740,7 +1738,6 @@
 narrateur|Maman a écouté.
 enfant-f|Je suis fière de mon effort.
 maman|Oui. Tu as porté l'arrosoir.
-maman|Bravo. C'est du bon travail.
 enfant-f|Puis les pots. Encore un effort.
 maman|Être fière, c'est content d'un effort.
 maman|Tu veux encore dire le mot ?
@@ -1783,7 +1780,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Honoré prend la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de maman. Ils rentrent.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila prend la main de maman. On rentre ? L'arrosoir reste ici. Oui. Il est moins lourd, vide. Tu as porté. Tu as aligné. Je suis encore fière. Bravo, Mila. Ils rentrent. L'escargot est encore sur sa feuille. Les tomates sentent toujours le soleil.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1958,12 +1955,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'étais fière de mon effort. L'arrosoir, puis les pots. Bravo. L'arrosoir vert reste près du bac. L'histoire est finie.</t>
+          <t>J'étais fière de mon effort. L'arrosoir, puis les pots. Bravo. L'arrosoir vert reste près du bac.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'étais fière de mon effort. L'arrosoir, puis les pots. Bravo. L'arrosoir vert reste près du bac.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2100,11 +2097,9 @@
         <is>
           <t>enfant-f|J'étais fière de mon effort.
 maman|L'arrosoir, puis les pots. Bravo.
-narrateur|L'arrosoir vert reste près du bac.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|L'arrosoir vert reste près du bac.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2123,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2168,6 +2163,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.010-07.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.010-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Honoré, maman</t>
+          <t>Mila, maman</t>
         </is>
       </c>
     </row>
